--- a/data/website.xlsx
+++ b/data/website.xlsx
@@ -68,7 +68,7 @@
     <t>Upcoming</t>
   </si>
   <si>
-    <t>Poster filename inside upcomingFolder. featured=yes selects the wide featured poster (at most one). home=yes includes a poster in the home rail. Titles are optional.</t>
+    <t>Poster filename inside upcomingFolder. Set featured=yes on one or more posters. Multiple featured posters form a slideshow in row order. home=yes includes a poster in the home rail. Titles are optional.</t>
   </si>
   <si>
     <t>BTS</t>

--- a/data/website.xlsx
+++ b/data/website.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2857" uniqueCount="1696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2861" uniqueCount="1698">
   <si>
     <t>Section</t>
   </si>
@@ -4101,6 +4101,12 @@
   </si>
   <si>
     <t>Gemini_Generated_Image_d59vdwd59vdwd59v.png</t>
+  </si>
+  <si>
+    <t>Feature1.png</t>
+  </si>
+  <si>
+    <t>RELEASING THIS MONTH</t>
   </si>
   <si>
     <t>UTTRAN BTS (16).png</t>
@@ -5646,60 +5652,60 @@
         <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>20</v>
@@ -5707,183 +5713,183 @@
     </row>
     <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="22" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="24" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="27" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="28" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="29" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="30" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="31" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
@@ -5891,650 +5897,650 @@
     </row>
     <row r="32" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="33" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="34" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="35" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="36" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="37" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="38" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="39" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="40" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="41" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="42" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="43" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="44" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="45" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="46" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="47" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="48" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="49" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="50" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="51" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="52" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="53" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="54" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="55" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="56" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="57" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="58" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="59" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="60" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="61" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="62" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="63" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="64" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="65" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="66" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="67" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="68" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="69" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="70" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="71" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="73" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="81" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="82" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="83" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="84" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="85" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="86" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="87" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="88" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="89" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="90" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="91" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="92" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="93" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="94" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="95" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="96" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="103" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="104" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="105" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="106" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="107" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="108" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="109" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="110" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="111" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="112" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
     </row>
   </sheetData>
@@ -6558,12 +6564,12 @@
         <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>76</v>
@@ -6571,23 +6577,23 @@
     </row>
     <row r="3" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>195</v>
@@ -6595,7 +6601,7 @@
     </row>
     <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>195</v>
@@ -6603,7 +6609,7 @@
     </row>
     <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>55</v>
@@ -6611,42 +6617,42 @@
     </row>
     <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
     </row>
   </sheetData>
@@ -14221,7 +14227,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="3" customWidth="1"/>
@@ -14439,8 +14445,22 @@
         <v>1345</v>
       </c>
     </row>
+    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>1345</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D15"/>
+  <autoFilter ref="A1:D16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -14465,7 +14485,7 @@
     </row>
     <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>55</v>
@@ -14473,7 +14493,7 @@
     </row>
     <row r="3" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>55</v>
@@ -14481,7 +14501,7 @@
     </row>
     <row r="4" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>55</v>
@@ -14489,7 +14509,7 @@
     </row>
     <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>55</v>
@@ -14497,7 +14517,7 @@
     </row>
     <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>55</v>
@@ -14505,7 +14525,7 @@
     </row>
     <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>55</v>
@@ -14513,7 +14533,7 @@
     </row>
     <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>55</v>
@@ -14521,7 +14541,7 @@
     </row>
     <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>55</v>
@@ -14529,7 +14549,7 @@
     </row>
     <row r="10" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>55</v>
@@ -14537,7 +14557,7 @@
     </row>
     <row r="11" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>55</v>
@@ -14545,7 +14565,7 @@
     </row>
     <row r="12" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>55</v>
@@ -14553,7 +14573,7 @@
     </row>
     <row r="13" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>55</v>
@@ -14561,7 +14581,7 @@
     </row>
     <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>55</v>
@@ -14569,7 +14589,7 @@
     </row>
     <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>55</v>
@@ -14577,7 +14597,7 @@
     </row>
     <row r="16" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>55</v>
@@ -14585,7 +14605,7 @@
     </row>
     <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>55</v>
@@ -14593,7 +14613,7 @@
     </row>
     <row r="18" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>55</v>
@@ -14601,7 +14621,7 @@
     </row>
     <row r="19" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>55</v>
@@ -14609,7 +14629,7 @@
     </row>
     <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>55</v>
@@ -14637,13 +14657,13 @@
         <v>56</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>32</v>
@@ -14651,155 +14671,155 @@
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>1396</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>1397</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>1394</v>
-      </c>
       <c r="D5" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>1407</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>1408</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>1404</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>1405</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
     </row>
   </sheetData>
@@ -14823,7 +14843,7 @@
         <v>56</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>29</v>
@@ -14834,86 +14854,86 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
     </row>
   </sheetData>
@@ -14937,120 +14957,120 @@
         <v>56</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>1450</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>1448</v>
-      </c>
       <c r="C3" s="5" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>1461</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>1459</v>
-      </c>
       <c r="C8" s="5" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
     </row>
   </sheetData>
